--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>117847462</v>
       </c>
       <c r="B2" t="n">
-        <v>56246</v>
+        <v>56338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117847462</v>
       </c>
       <c r="B2" t="n">
-        <v>56338</v>
+        <v>56432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117847462</v>
       </c>
       <c r="B2" t="n">
-        <v>56432</v>
+        <v>56435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392290</v>
+        <v>124392344</v>
       </c>
       <c r="B4" t="n">
-        <v>56466</v>
+        <v>56492</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,44 +932,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100070</v>
+        <v>208260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523689</v>
+        <v>523579</v>
       </c>
       <c r="R4" t="n">
-        <v>6228642</v>
+        <v>6228662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392344</v>
+        <v>124392290</v>
       </c>
       <c r="B5" t="n">
-        <v>56492</v>
+        <v>56466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,40 +1053,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>100070</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523579</v>
+        <v>523689</v>
       </c>
       <c r="R5" t="n">
-        <v>6228662</v>
+        <v>6228642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392359</v>
+        <v>124392290</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
+        <v>56466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,40 +811,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523624</v>
+        <v>523689</v>
       </c>
       <c r="R3" t="n">
-        <v>6228661</v>
+        <v>6228642</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +896,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1041,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392290</v>
+        <v>124392359</v>
       </c>
       <c r="B5" t="n">
-        <v>56466</v>
+        <v>56471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,44 +1057,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100070</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523689</v>
+        <v>523624</v>
       </c>
       <c r="R5" t="n">
-        <v>6228642</v>
+        <v>6228661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392290</v>
+        <v>124392359</v>
       </c>
       <c r="B3" t="n">
-        <v>56466</v>
+        <v>56471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,44 +811,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100070</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523689</v>
+        <v>523624</v>
       </c>
       <c r="R3" t="n">
-        <v>6228642</v>
+        <v>6228661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392359</v>
+        <v>124392290</v>
       </c>
       <c r="B5" t="n">
-        <v>56471</v>
+        <v>56466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,40 +1053,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523624</v>
+        <v>523689</v>
       </c>
       <c r="R5" t="n">
-        <v>6228661</v>
+        <v>6228642</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392359</v>
+        <v>124392344</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
+        <v>56492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523624</v>
+        <v>523579</v>
       </c>
       <c r="R3" t="n">
-        <v>6228661</v>
+        <v>6228662</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392344</v>
+        <v>124392290</v>
       </c>
       <c r="B4" t="n">
-        <v>56492</v>
+        <v>56466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,40 +932,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208260</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523579</v>
+        <v>523689</v>
       </c>
       <c r="R4" t="n">
-        <v>6228662</v>
+        <v>6228642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392290</v>
+        <v>124392359</v>
       </c>
       <c r="B5" t="n">
-        <v>56466</v>
+        <v>56471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,44 +1057,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100070</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523689</v>
+        <v>523624</v>
       </c>
       <c r="R5" t="n">
-        <v>6228642</v>
+        <v>6228661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392344</v>
+        <v>124392359</v>
       </c>
       <c r="B3" t="n">
-        <v>56492</v>
+        <v>56471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523579</v>
+        <v>523624</v>
       </c>
       <c r="R3" t="n">
-        <v>6228662</v>
+        <v>6228661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392359</v>
+        <v>124392344</v>
       </c>
       <c r="B5" t="n">
-        <v>56471</v>
+        <v>56492</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,26 +1061,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523624</v>
+        <v>523579</v>
       </c>
       <c r="R5" t="n">
-        <v>6228661</v>
+        <v>6228662</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392359</v>
+        <v>124392344</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
+        <v>56492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523624</v>
+        <v>523579</v>
       </c>
       <c r="R3" t="n">
-        <v>6228661</v>
+        <v>6228662</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392344</v>
+        <v>124392359</v>
       </c>
       <c r="B5" t="n">
-        <v>56492</v>
+        <v>56471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,26 +1061,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523579</v>
+        <v>523624</v>
       </c>
       <c r="R5" t="n">
-        <v>6228662</v>
+        <v>6228661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392290</v>
+        <v>124392359</v>
       </c>
       <c r="B4" t="n">
-        <v>56466</v>
+        <v>56471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,44 +932,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100070</v>
+        <v>208255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523689</v>
+        <v>523624</v>
       </c>
       <c r="R4" t="n">
-        <v>6228642</v>
+        <v>6228661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392359</v>
+        <v>124392290</v>
       </c>
       <c r="B5" t="n">
-        <v>56471</v>
+        <v>56466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,40 +1053,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523624</v>
+        <v>523689</v>
       </c>
       <c r="R5" t="n">
-        <v>6228661</v>
+        <v>6228642</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392344</v>
+        <v>124392359</v>
       </c>
       <c r="B3" t="n">
-        <v>56492</v>
+        <v>56471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523579</v>
+        <v>523624</v>
       </c>
       <c r="R3" t="n">
-        <v>6228662</v>
+        <v>6228661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392359</v>
+        <v>124392290</v>
       </c>
       <c r="B4" t="n">
-        <v>56471</v>
+        <v>56466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,40 +932,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523624</v>
+        <v>523689</v>
       </c>
       <c r="R4" t="n">
-        <v>6228661</v>
+        <v>6228642</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392290</v>
+        <v>124392344</v>
       </c>
       <c r="B5" t="n">
-        <v>56466</v>
+        <v>56492</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,44 +1057,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100070</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523689</v>
+        <v>523579</v>
       </c>
       <c r="R5" t="n">
-        <v>6228642</v>
+        <v>6228662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124392359</v>
+        <v>124392290</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
+        <v>56466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,40 +811,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523624</v>
+        <v>523689</v>
       </c>
       <c r="R3" t="n">
-        <v>6228661</v>
+        <v>6228642</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +896,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Vilande i solen, ömssskinn intill.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392290</v>
+        <v>124392359</v>
       </c>
       <c r="B4" t="n">
-        <v>56466</v>
+        <v>56471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,44 +936,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100070</v>
+        <v>208255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523689</v>
+        <v>523624</v>
       </c>
       <c r="R4" t="n">
-        <v>6228642</v>
+        <v>6228661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vilande i solen, ömssskinn intill.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>128250662</v>
       </c>
       <c r="B6" t="n">
-        <v>56607</v>
+        <v>56619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>128250662</v>
       </c>
       <c r="B6" t="n">
-        <v>56619</v>
+        <v>56623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>128250662</v>
       </c>
       <c r="B6" t="n">
-        <v>56623</v>
+        <v>56650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41702-2021 artfynd.xlsx
+++ b/artfynd/A 41702-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117847462</v>
       </c>
       <c r="B2" t="n">
-        <v>56435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,12 +797,7 @@
         <v>124392290</v>
       </c>
       <c r="B3" t="n">
-        <v>56466</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,49 +914,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124392359</v>
+        <v>124392323</v>
       </c>
       <c r="B4" t="n">
-        <v>56471</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -977,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523624</v>
+        <v>523676</v>
       </c>
       <c r="R4" t="n">
-        <v>6228661</v>
+        <v>6228612</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,14 +994,14 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I hög ljung.</t>
+          <t>Trolig sandödla som försvann hastigt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -1045,15 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124392344</v>
+        <v>124392359</v>
       </c>
       <c r="B5" t="n">
-        <v>56492</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,26 +1033,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1098,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523579</v>
+        <v>523624</v>
       </c>
       <c r="R5" t="n">
-        <v>6228662</v>
+        <v>6228661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1110,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+          <t>I hög ljung.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1141,7 @@
         <v>128250662</v>
       </c>
       <c r="B6" t="n">
-        <v>56650</v>
+        <v>56884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,6 +1246,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124392344</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björketorp, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523579</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6228662</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Listerby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två ex tillsammans i hög ljung strax SO om fornlämningen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
